--- a/Data Management MasterClass/Data Quality Assessment Framework.xlsx
+++ b/Data Management MasterClass/Data Quality Assessment Framework.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jansr\Downloads\Miscellaneous_Technologies\Data Management MasterClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DFF079F-F340-4415-83A9-63A44637D865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB552409-D432-4F99-A8CD-274FB2019D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AC149533-716C-46FA-A130-E7174D6DDE9B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data Quality Framework" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
-  <si>
-    <t xml:space="preserve">Data Quality Management </t>
-  </si>
-  <si>
-    <t>Verify access through SQL query execution on the data warehouse platform</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
   <si>
     <t>Indexing</t>
   </si>
@@ -48,15 +42,9 @@
     <t>ETL Process</t>
   </si>
   <si>
-    <t>Ensure the data is available and accessible after the successful transformation and load process.</t>
-  </si>
-  <si>
     <t>Security and Permissions</t>
   </si>
   <si>
-    <t>SQL Access</t>
-  </si>
-  <si>
     <t>Verify indexing on large fact tables to ensure fast query execution, and maintain indexes as data grows.</t>
   </si>
   <si>
@@ -85,6 +73,54 @@
   </si>
   <si>
     <t>Ensure that rounding or truncation errors are avoided and that data maintains the appropriate precision.</t>
+  </si>
+  <si>
+    <t>Edge Cases and Boundary Values</t>
+  </si>
+  <si>
+    <t>Aggregation</t>
+  </si>
+  <si>
+    <t>Ensure that edge cases, such as very small or large values, null values, and outliers, are handled accurately during transformations based on the business rules.</t>
+  </si>
+  <si>
+    <t>Ensure that the data loaded into the dimension tables is correct and reflects the true values from the source systems.</t>
+  </si>
+  <si>
+    <t>Ensure that the data loaded into fact tables is accurate and matches the source data after transformation.</t>
+  </si>
+  <si>
+    <t>Slowly Changing Dimensions</t>
+  </si>
+  <si>
+    <t>Ensure that data changes in slowly changing dimensions are accurately reflected in the dimension and fact tables.</t>
+  </si>
+  <si>
+    <t>Accuracy Reconciliation</t>
+  </si>
+  <si>
+    <t>Completeness Reconciliation</t>
+  </si>
+  <si>
+    <t>Dimension Data Integrity</t>
+  </si>
+  <si>
+    <t>During ETL, ensure that data is standardized to remove discrepancies, such as name case differences (john doe vs. John Doe), formatting inconsistencies (e.g., date formats), and inconsistent units.</t>
+  </si>
+  <si>
+    <t>Data Harmonization</t>
+  </si>
+  <si>
+    <t>Foreign Key and Referential Integrity</t>
+  </si>
+  <si>
+    <t>Ensure foreign keys in fact tables point to valid records in dimension tables. This prevents issues like orphaned records or mismatched relationships.</t>
+  </si>
+  <si>
+    <t>Ensure data retrieval times are acceptable for large datasets and concurrent queries, and that the warehouse can scale when data volume increases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Quality Framework </t>
   </si>
   <si>
     <r>
@@ -153,70 +189,19 @@
     </r>
   </si>
   <si>
-    <t>Edge Cases and Boundary Values</t>
-  </si>
-  <si>
-    <t>Aggregation</t>
-  </si>
-  <si>
-    <t>Ensure that edge cases, such as very small or large values, null values, and outliers, are handled accurately during transformations based on the business rules.</t>
-  </si>
-  <si>
-    <t>Ensure that the data loaded into the dimension tables is correct and reflects the true values from the source systems.</t>
-  </si>
-  <si>
-    <t>Ensure that the data loaded into fact tables is accurate and matches the source data after transformation.</t>
-  </si>
-  <si>
-    <t>Slowly Changing Dimensions</t>
-  </si>
-  <si>
-    <t>Ensure that data changes in slowly changing dimensions are accurately reflected in the dimension and fact tables.</t>
-  </si>
-  <si>
-    <t>Accuracy Reconciliation</t>
-  </si>
-  <si>
-    <t>Completeness Reconciliation</t>
-  </si>
-  <si>
-    <t>Row Count Validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare the number of rows in the source system with the number of rows in the data warehouse for each table. </t>
-  </si>
-  <si>
-    <t>Dimension Data Integrity</t>
-  </si>
-  <si>
-    <t>During ETL, ensure that data is standardized to remove discrepancies, such as name case differences (john doe vs. John Doe), formatting inconsistencies (e.g., date formats), and inconsistent units.</t>
-  </si>
-  <si>
-    <t>Data Harmonization</t>
-  </si>
-  <si>
-    <t>Foreign Key and Referential Integrity</t>
-  </si>
-  <si>
-    <t>Ensure foreign keys in fact tables point to valid records in dimension tables. This prevents issues like orphaned records or mismatched relationships.</t>
-  </si>
-  <si>
-    <t>Dimension Data</t>
-  </si>
-  <si>
-    <t>Fact Data</t>
-  </si>
-  <si>
-    <t>Ensure data retrieval times are acceptable for large datasets and concurrent queries, and that the warehouse can scale when data volume increases.</t>
-  </si>
-  <si>
-    <t>Ensure all records exist in the target system at the correct granularity without missing records or duplicates.</t>
-  </si>
-  <si>
-    <t>Ensure that dimension tables do not contain null, blank, or duplicate records or values</t>
-  </si>
-  <si>
-    <t>Ensure that the data in the warehouse matches the corresponding data in the source system for random sample of 16 accounts.</t>
+    <t>Validate that outdated or irrelevant data is excluded or archived during transformation and load.</t>
+  </si>
+  <si>
+    <t>Business Rules Alignment</t>
+  </si>
+  <si>
+    <t>Ensure datasets align with updated business definitions and reporting needs.</t>
+  </si>
+  <si>
+    <t>Data Deprecation</t>
+  </si>
+  <si>
+    <t>Identify and flag obsolete data sources and fields for decommissioning.</t>
   </si>
   <si>
     <r>
@@ -281,7 +266,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> - Ensure that data in the data warehouse is easily accessible and can be queried efficiently by the data governance and reporting teams.</t>
+      <t xml:space="preserve"> - Data in the data warehouse is easily accessible and can be queried efficiently by the data governance and reporting teams.</t>
     </r>
   </si>
   <si>
@@ -347,7 +332,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> - Ensure that the data in the data warehouse is complete, with no missing records, incomplete entries, or duplicates, and is available at the required granularity.</t>
+      <t xml:space="preserve"> - Data in the data warehouse is complete, with no missing records, incomplete entries, or duplicates, and is available at the required granularity.</t>
     </r>
   </si>
   <si>
@@ -413,15 +398,363 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> - Ensures that the same data is represented consistently across all systems and adheres to predefined business rules and constraints.</t>
-    </r>
+      <t xml:space="preserve"> - The same data is represented consistently across all systems and adheres to predefined business rules and constraints.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Relevance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - The data reflects the current business context and requirements, avoiding outdated or no longer useful information.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Timeliness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -  The data is up to date and available within required timeframes to support decision-making.</t>
+    </r>
+  </si>
+  <si>
+    <t>Confirm data loads are scheduled and completed within acceptable latency thresholds.</t>
+  </si>
+  <si>
+    <t>ETL Scheduling</t>
+  </si>
+  <si>
+    <t>Timestamp Validation</t>
+  </si>
+  <si>
+    <t>Validate that data timestamps are accurate, reflect the true event or transaction times, and maintain the intended time zone and logical chronological(time based on ordered events) order.</t>
+  </si>
+  <si>
+    <t>Dimension Table Data</t>
+  </si>
+  <si>
+    <t>Fact Table Data</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Uniqueness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -  The data records are distinct and free from duplicates, particularly where uniqueness is required by design.</t>
+    </r>
+  </si>
+  <si>
+    <t>ETL Deduplication</t>
+  </si>
+  <si>
+    <t>Surrogate Key Management</t>
+  </si>
+  <si>
+    <t>Ensure logic is implemented to detect and eliminate duplicates during data transformation.</t>
+  </si>
+  <si>
+    <t>Surrogate keys are properly used to track uniqueness in slowly changing dimension records.</t>
+  </si>
+  <si>
+    <t>Surrogate Key(Primary Key) Constraints</t>
+  </si>
+  <si>
+    <t>Validate that surrogate keys are enforced and not violated in fact and dimension tables.
+1.No two rows have the same record based surrogate keys in fact and dimension table.
+2.Surrogate key fields are not null.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Validity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -  The individual data values are logically correct, meet business rules, and conform to required formats.
+Example:
+A person's age must be a number between 0 and 120.
+A product code must match a defined pattern (e.g., ABC-123).
+Dates must be valid (e.g., 2025-02-30 is invalid because February 30th doesn’t exist).</t>
+    </r>
+  </si>
+  <si>
+    <t>ETL Validation Rules</t>
+  </si>
+  <si>
+    <t>Ensure transformations are applied to enforce acceptable ranges, data types, and value formats.</t>
+  </si>
+  <si>
+    <t>Domain Validation</t>
+  </si>
+  <si>
+    <t>Confirm that values fall within accepted domain lists (e.g., valid countries, product categories).</t>
+  </si>
+  <si>
+    <t>Fact Data Integrity</t>
+  </si>
+  <si>
+    <t>Business Rule Logic</t>
+  </si>
+  <si>
+    <t>Validate field-level business logic (e.g., invoice amount ≥ 0, end date &gt; start date).</t>
+  </si>
+  <si>
+    <t>Format Enforcement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensure standardized formatting (e.g. date formats, currency symbols, phone number formats).</t>
+  </si>
+  <si>
+    <t>Ensure the data is available and accessible through SQL query after the successful transformation and load process.</t>
+  </si>
+  <si>
+    <t>Ensure that the data in the warehouse matches the corresponding data in the source system for a random sample of records.</t>
+  </si>
+  <si>
+    <t>Ensure all records exist in the target system at the correct granularity (i.e., data is loaded at the appropriate level of detail) without missing records or duplicates. Include checks for row count consistency between the source and target systems.</t>
+  </si>
+  <si>
+    <t>Ensure that fact tables contain all necessary data and that critical fields, such as keys and metrics, are populated and non-null.</t>
+  </si>
+  <si>
+    <t>Ensure that dimension tables do not contain missing, null, or duplicate records and adhere to business rules.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +786,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -463,24 +803,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF007E39"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor rgb="FF005828"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -512,24 +852,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -537,24 +864,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,6 +891,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFEF5F0"/>
+      <color rgb="FF005828"/>
       <color rgb="FF007E39"/>
     </mruColors>
   </colors>
@@ -874,216 +1204,353 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB321605-9636-4598-B3B1-ECD7B20DEBB9}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.6328125" customWidth="1"/>
-    <col min="2" max="2" width="125.90625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="121.08984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" ht="47" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="9"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="9"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="9"/>
+    </row>
+    <row r="8" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="10"/>
+    </row>
+    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="9"/>
+    </row>
+    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16" spans="1:3" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="9"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="9"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="9"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="9"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="9"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="8"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="C29" s="9"/>
+    </row>
+    <row r="30" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="10"/>
-    </row>
-    <row r="22" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="1:3" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="8"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="9"/>
+    </row>
+    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="9"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="8"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="9"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="9"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A20:B20"/>
+  <mergeCells count="9">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data Management MasterClass/Data Quality Assessment Framework.xlsx
+++ b/Data Management MasterClass/Data Quality Assessment Framework.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jansr\Downloads\Miscellaneous_Technologies\Data Management MasterClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB552409-D432-4F99-A8CD-274FB2019D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{367316C1-76E0-48A0-ADBA-462E4FAFEE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AC149533-716C-46FA-A130-E7174D6DDE9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Quality Framework" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Quality Framework'!$A$4:$F$41</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="75">
   <si>
     <t>Indexing</t>
   </si>
@@ -54,12 +57,6 @@
     <t>Ensure that access control mechanisms are working as expected and that users only have access to the data they’re authorized to view.</t>
   </si>
   <si>
-    <t>Questions</t>
-  </si>
-  <si>
-    <t>Only for databricks?</t>
-  </si>
-  <si>
     <t>Reporting Tool Integration</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
   </si>
   <si>
     <t>Ensure data retrieval times are acceptable for large datasets and concurrent queries, and that the warehouse can scale when data volume increases.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Quality Framework </t>
   </si>
   <si>
     <r>
@@ -195,9 +189,6 @@
     <t>Business Rules Alignment</t>
   </si>
   <si>
-    <t>Ensure datasets align with updated business definitions and reporting needs.</t>
-  </si>
-  <si>
     <t>Data Deprecation</t>
   </si>
   <si>
@@ -270,270 +261,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Data Quality Dimension</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Completeness</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Data in the data warehouse is complete, with no missing records, incomplete entries, or duplicates, and is available at the required granularity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Data Quality Dimension</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Consistency</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - The same data is represented consistently across all systems and adheres to predefined business rules and constraints.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Data Quality Dimension</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Relevance</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - The data reflects the current business context and requirements, avoiding outdated or no longer useful information.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Data Quality Dimension</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Timeliness</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -  The data is up to date and available within required timeframes to support decision-making.</t>
-    </r>
-  </si>
-  <si>
     <t>Confirm data loads are scheduled and completed within acceptable latency thresholds.</t>
   </si>
   <si>
@@ -550,72 +277,6 @@
   </si>
   <si>
     <t>Fact Table Data</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Data Quality Dimension</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Uniqueness</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -  The data records are distinct and free from duplicates, particularly where uniqueness is required by design.</t>
-    </r>
   </si>
   <si>
     <t>ETL Deduplication</t>
@@ -636,6 +297,372 @@
     <t>Validate that surrogate keys are enforced and not violated in fact and dimension tables.
 1.No two rows have the same record based surrogate keys in fact and dimension table.
 2.Surrogate key fields are not null.</t>
+  </si>
+  <si>
+    <t>ETL Validation Rules</t>
+  </si>
+  <si>
+    <t>Ensure transformations are applied to enforce acceptable ranges, data types, and value formats.</t>
+  </si>
+  <si>
+    <t>Domain Validation</t>
+  </si>
+  <si>
+    <t>Confirm that values fall within accepted domain lists (e.g., valid countries, product categories).</t>
+  </si>
+  <si>
+    <t>Fact Data Integrity</t>
+  </si>
+  <si>
+    <t>Business Rule Logic</t>
+  </si>
+  <si>
+    <t>Validate field-level business logic (e.g., invoice amount ≥ 0, end date &gt; start date).</t>
+  </si>
+  <si>
+    <t>Format Enforcement</t>
+  </si>
+  <si>
+    <t>Ensure the data is available and accessible through SQL query after the successful transformation and load process.</t>
+  </si>
+  <si>
+    <t>Ensure that the data in the warehouse matches the corresponding data in the source system for a random sample of records.</t>
+  </si>
+  <si>
+    <t>Ensure that fact tables contain all necessary data and that critical fields, such as keys and metrics, are populated and non-null.</t>
+  </si>
+  <si>
+    <t>Ensure that dimension tables do not contain missing, null, or duplicate records and adhere to business rules.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completeness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Data in the data warehouse is complete, with no missing records, incomplete entries, or duplicates, and is available at the required granularity.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Consistency</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - The same data is represented consistently across all systems and adheres to predefined business rules and constraints.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Relevance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - The data reflects the current business context and requirements, avoiding outdated or no longer useful information.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Timeliness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -  The data is up to date and available within required timeframes to support decision-making.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Uniqueness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -  The data records are distinct and free from duplicates, particularly where uniqueness is required by design.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -708,53 +735,64 @@
     </r>
   </si>
   <si>
-    <t>ETL Validation Rules</t>
-  </si>
-  <si>
-    <t>Ensure transformations are applied to enforce acceptable ranges, data types, and value formats.</t>
-  </si>
-  <si>
-    <t>Domain Validation</t>
-  </si>
-  <si>
-    <t>Confirm that values fall within accepted domain lists (e.g., valid countries, product categories).</t>
-  </si>
-  <si>
-    <t>Fact Data Integrity</t>
-  </si>
-  <si>
-    <t>Business Rule Logic</t>
-  </si>
-  <si>
-    <t>Validate field-level business logic (e.g., invoice amount ≥ 0, end date &gt; start date).</t>
-  </si>
-  <si>
-    <t>Format Enforcement</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ensure standardized formatting (e.g. date formats, currency symbols, phone number formats).</t>
-  </si>
-  <si>
-    <t>Ensure the data is available and accessible through SQL query after the successful transformation and load process.</t>
-  </si>
-  <si>
-    <t>Ensure that the data in the warehouse matches the corresponding data in the source system for a random sample of records.</t>
-  </si>
-  <si>
-    <t>Ensure all records exist in the target system at the correct granularity (i.e., data is loaded at the appropriate level of detail) without missing records or duplicates. Include checks for row count consistency between the source and target systems.</t>
-  </si>
-  <si>
-    <t>Ensure that fact tables contain all necessary data and that critical fields, such as keys and metrics, are populated and non-null.</t>
-  </si>
-  <si>
-    <t>Ensure that dimension tables do not contain missing, null, or duplicate records and adhere to business rules.</t>
+    <t>Ensure standardized formatting (e.g. date formats, currency symbols, phone number formats).</t>
+  </si>
+  <si>
+    <t>Ensure datasets align with updated business definitions and reporting needs. For example, if the business definition for calculating revenue is updated, the corresponding transformation logic in the ETL process should also be updated to reflect this change.</t>
+  </si>
+  <si>
+    <t>Monthly Reconciliation</t>
+  </si>
+  <si>
+    <t>UAT Testing</t>
+  </si>
+  <si>
+    <t>Colocation Testing</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Ensure all records exist in the target system at the correct granularity (i.e., data is loaded at the appropriate level of detail and not summarized) without missing records or duplicates. Include checks for row count consistency between the source and target systems.</t>
+  </si>
+  <si>
+    <t>Data Governance Projects</t>
+  </si>
+  <si>
+    <r>
+      <t>Data Quality Assessment Framework</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Data Governance Team
+5/8/2025</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> ü</t>
+  </si>
+  <si>
+    <t>This framework provides a consolidated list of data quality dimensions that the Data Governance team uses for validation and testing across multiple environments and processes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,8 +831,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Wingdings"/>
+      <charset val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -809,18 +882,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF005828"/>
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF345222"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -852,36 +937,141 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -891,6 +1081,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF345222"/>
+      <color rgb="FF2B441C"/>
+      <color rgb="FFFFF8E5"/>
+      <color rgb="FFFEF2EC"/>
       <color rgb="FFFEF5F0"/>
       <color rgb="FF005828"/>
       <color rgb="FF007E39"/>
@@ -1204,353 +1398,520 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB321605-9636-4598-B3B1-ECD7B20DEBB9}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="121.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="1" max="1" width="51.1796875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="76.81640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="20.26953125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="15"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" s="6" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="20" spans="1:6" ht="59" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:6" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2" spans="1:3" ht="47" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="11"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="9"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="9"/>
-    </row>
-    <row r="8" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="10"/>
-    </row>
-    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="9"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="11"/>
+    </row>
+    <row r="35" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="9"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="9"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="9"/>
-    </row>
-    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="9"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="9"/>
-    </row>
-    <row r="16" spans="1:3" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="10"/>
-    </row>
-    <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="9"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="9"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="9"/>
-    </row>
-    <row r="28" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="8"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:3" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="8"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="9"/>
-    </row>
-    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="9"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" spans="1:3" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="8"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="9"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="9"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="B41" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="3"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:B16"/>
+  <autoFilter ref="A4:F41" xr:uid="{FB321605-9636-4598-B3B1-ECD7B20DEBB9}"/>
+  <mergeCells count="13">
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data Management MasterClass/Data Quality Assessment Framework.xlsx
+++ b/Data Management MasterClass/Data Quality Assessment Framework.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jansr\Downloads\Miscellaneous_Technologies\Data Management MasterClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{367316C1-76E0-48A0-ADBA-462E4FAFEE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A72F961-119F-4264-AE92-AE930505A7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AC149533-716C-46FA-A130-E7174D6DDE9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Quality Framework" sheetId="1" r:id="rId1"/>
+    <sheet name="DropDownOptions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Quality Framework'!$A$4:$F$41</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="77">
   <si>
     <t>Indexing</t>
   </si>
@@ -747,16 +748,7 @@
     <t>UAT Testing</t>
   </si>
   <si>
-    <t>Colocation Testing</t>
-  </si>
-  <si>
     <t>Remarks</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Description</t>
   </si>
   <si>
     <t>Ensure all records exist in the target system at the correct granularity (i.e., data is loaded at the appropriate level of detail and not summarized) without missing records or duplicates. Include checks for row count consistency between the source and target systems.</t>
@@ -782,17 +774,32 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> ü</t>
-  </si>
-  <si>
     <t>This framework provides a consolidated list of data quality dimensions that the Data Governance team uses for validation and testing across multiple environments and processes.</t>
+  </si>
+  <si>
+    <t>Validation Criteria</t>
+  </si>
+  <si>
+    <t>Validation Criteria Description</t>
+  </si>
+  <si>
+    <t>Co-location Testing</t>
+  </si>
+  <si>
+    <t>Applicable</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Included as it can be useful when we are testing the schemas in Databricks.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -826,13 +833,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -859,12 +859,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="9" tint="-0.499984740745262"/>
-      <name val="Wingdings"/>
-      <charset val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1013,65 +1007,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1401,518 +1398,657 @@
   <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="76.81640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="20.26953125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="51.1796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="76.81640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" customWidth="1"/>
+    <col min="5" max="6" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+    </row>
+    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="C3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="14"/>
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" spans="1:6" s="5" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="19"/>
+    </row>
+    <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="F6" s="22"/>
+    </row>
+    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="22"/>
+    </row>
+    <row r="8" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="22"/>
+    </row>
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="22"/>
+    </row>
+    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="22"/>
+    </row>
+    <row r="11" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+    </row>
+    <row r="12" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="22"/>
+    </row>
+    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="22"/>
+    </row>
+    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="22"/>
+    </row>
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="22"/>
+    </row>
+    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="22"/>
+    </row>
+    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="22"/>
+    </row>
+    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="22"/>
+    </row>
+    <row r="19" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+    </row>
+    <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="16"/>
-    </row>
-    <row r="4" spans="1:6" s="6" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="22"/>
+    </row>
+    <row r="21" spans="1:6" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="19"/>
+    </row>
+    <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="22"/>
+    </row>
+    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="22"/>
+    </row>
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="22"/>
+    </row>
+    <row r="27" spans="1:6" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="19"/>
+    </row>
+    <row r="28" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" spans="1:6" ht="59" x14ac:dyDescent="0.45">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="1:6" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
-    </row>
-    <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:6" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="22"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="11"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="19"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="22"/>
     </row>
     <row r="33" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="22"/>
     </row>
     <row r="34" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="11"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="19"/>
     </row>
     <row r="35" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="22"/>
     </row>
     <row r="36" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="22"/>
     </row>
     <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="22"/>
     </row>
     <row r="38" spans="1:6" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="11"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="19"/>
     </row>
     <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="22"/>
     </row>
     <row r="40" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" s="22"/>
     </row>
     <row r="41" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:F41" xr:uid="{FB321605-9636-4598-B3B1-ECD7B20DEBB9}"/>
   <mergeCells count="13">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{14409448-5206-4060-B79C-B4B9879F0DF1}">
+          <x14:formula1>
+            <xm:f>DropDownOptions!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>D20:F20 D6:F10 D12:F18 D22:F26 D28:F30 D32:F33 D35:F37 D39:F41</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57741DD1-CE7D-4ECA-AC24-1475F7767330}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data Management MasterClass/Data Quality Assessment Framework.xlsx
+++ b/Data Management MasterClass/Data Quality Assessment Framework.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jansr\Downloads\Miscellaneous_Technologies\Data Management MasterClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A72F961-119F-4264-AE92-AE930505A7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A04CBA1-92A5-44D2-A7C1-718C05562338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AC149533-716C-46FA-A130-E7174D6DDE9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Quality Framework" sheetId="1" r:id="rId1"/>
-    <sheet name="DropDownOptions" sheetId="2" r:id="rId2"/>
+    <sheet name="DropDownOptions" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Quality Framework'!$A$4:$F$41</definedName>
@@ -196,72 +196,6 @@
     <t>Identify and flag obsolete data sources and fields for decommissioning.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Data Quality Dimension</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accessibility</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Data in the data warehouse is easily accessible and can be queried efficiently by the data governance and reporting teams.</t>
-    </r>
-  </si>
-  <si>
     <t>Confirm data loads are scheduled and completed within acceptable latency thresholds.</t>
   </si>
   <si>
@@ -793,6 +727,72 @@
   </si>
   <si>
     <t>Included as it can be useful when we are testing the schemas in Databricks.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Quality Dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accessibility</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Data in the data warehouse is easily accessible and can be queried efficiently by the Data Governance and Reporting teams.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1031,6 +1031,27 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1048,27 +1069,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1407,7 +1407,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
@@ -1416,69 +1416,69 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+    </row>
+    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-    </row>
-    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="B3" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="21"/>
+      <c r="F3" s="22"/>
+    </row>
+    <row r="4" spans="1:6" s="5" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
-    </row>
-    <row r="4" spans="1:6" s="5" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="5" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
+      <c r="A5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="22"/>
+        <v>51</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -1488,13 +1488,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="22"/>
+      <c r="D7" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -1503,16 +1503,16 @@
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="22" t="s">
+      <c r="C8" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="22"/>
+      <c r="D8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="22"/>
+      <c r="D9" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -1538,23 +1538,23 @@
         <v>7</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="22"/>
+      <c r="D10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15"/>
     </row>
     <row r="12" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -1564,45 +1564,45 @@
         <v>8</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="22"/>
+      <c r="D12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="22"/>
+      <c r="D13" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="22"/>
+      <c r="D14" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -1612,29 +1612,29 @@
         <v>10</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="22"/>
+      <c r="D15" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="22"/>
+      <c r="D16" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -1644,13 +1644,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="22"/>
+      <c r="D17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -1660,49 +1660,49 @@
         <v>17</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="22"/>
+      <c r="D18" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="19"/>
+      <c r="A19" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="22"/>
+      <c r="D20" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="19"/>
+      <c r="A21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="15"/>
     </row>
     <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
@@ -1712,13 +1712,13 @@
         <v>21</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="22"/>
+      <c r="D22" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
@@ -1728,71 +1728,71 @@
         <v>24</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="22"/>
+      <c r="D23" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="22"/>
+      <c r="D24" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="22"/>
+      <c r="D25" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="22"/>
+      <c r="D26" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="19"/>
+      <c r="A27" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
     </row>
     <row r="28" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
@@ -1802,29 +1802,29 @@
         <v>27</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="22"/>
+      <c r="D28" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="22"/>
+      <c r="D29" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="11"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
@@ -1834,175 +1834,178 @@
         <v>30</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="22"/>
+      <c r="D30" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="19"/>
+      <c r="A31" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="15"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="22"/>
+      <c r="D32" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="22"/>
+      <c r="D33" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="19"/>
+      <c r="A34" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="15"/>
     </row>
     <row r="35" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F35" s="22"/>
+      <c r="D35" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="22"/>
+      <c r="D36" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" s="4"/>
-      <c r="D37" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" s="22"/>
+      <c r="D37" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="19"/>
+      <c r="A38" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
     </row>
     <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="22"/>
+      <c r="D39" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="11"/>
     </row>
     <row r="40" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F40" s="22"/>
+      <c r="D40" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" s="11"/>
     </row>
     <row r="41" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41" s="4"/>
-      <c r="D41" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F41" s="22"/>
+      <c r="D41" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:F41" xr:uid="{FB321605-9636-4598-B3B1-ECD7B20DEBB9}"/>
   <mergeCells count="13">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2013,9 +2016,6 @@
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2040,12 +2040,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Data Management MasterClass/Data Quality Assessment Framework.xlsx
+++ b/Data Management MasterClass/Data Quality Assessment Framework.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jansr\Downloads\Miscellaneous_Technologies\Data Management MasterClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A04CBA1-92A5-44D2-A7C1-718C05562338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C49B09-C45D-4974-85FC-43A66123EFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AC149533-716C-46FA-A130-E7174D6DDE9B}"/>
   </bookViews>
@@ -682,9 +682,6 @@
     <t>UAT Testing</t>
   </si>
   <si>
-    <t>Remarks</t>
-  </si>
-  <si>
     <t>Ensure all records exist in the target system at the correct granularity (i.e., data is loaded at the appropriate level of detail and not summarized) without missing records or duplicates. Include checks for row count consistency between the source and target systems.</t>
   </si>
   <si>
@@ -726,9 +723,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Included as it can be useful when we are testing the schemas in Databricks.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i/>
@@ -793,6 +787,12 @@
       </rPr>
       <t xml:space="preserve"> - Data in the data warehouse is easily accessible and can be queried efficiently by the Data Governance and Reporting teams.</t>
     </r>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>JS 5/8: Included as it can be useful when we are testing the schemas in Databricks.</t>
   </si>
 </sst>
 </file>
@@ -1037,6 +1037,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1066,9 +1069,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1407,7 +1407,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
@@ -1416,35 +1416,35 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-    </row>
-    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="22"/>
+      <c r="C3" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
     </row>
     <row r="4" spans="1:6" s="5" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
         <v>63</v>
       </c>
@@ -1452,18 +1452,18 @@
         <v>64</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
+      <c r="A5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -1473,10 +1473,10 @@
         <v>51</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="11"/>
     </row>
@@ -1489,14 +1489,14 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="11"/>
     </row>
-    <row r="8" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -1504,13 +1504,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="11"/>
     </row>
@@ -1523,10 +1523,10 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="11"/>
     </row>
@@ -1539,22 +1539,22 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -1565,10 +1565,10 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F12" s="11"/>
     </row>
@@ -1581,10 +1581,10 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F13" s="11"/>
     </row>
@@ -1597,10 +1597,10 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" s="11"/>
     </row>
@@ -1613,10 +1613,10 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F15" s="11"/>
     </row>
@@ -1629,10 +1629,10 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" s="11"/>
     </row>
@@ -1645,10 +1645,10 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" s="11"/>
     </row>
@@ -1661,48 +1661,48 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
@@ -1713,10 +1713,10 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="11"/>
     </row>
@@ -1729,10 +1729,10 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F23" s="11"/>
     </row>
@@ -1745,10 +1745,10 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F24" s="11"/>
     </row>
@@ -1761,10 +1761,10 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F25" s="11"/>
     </row>
@@ -1777,22 +1777,22 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
@@ -1803,10 +1803,10 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F28" s="11"/>
     </row>
@@ -1819,10 +1819,10 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F29" s="11"/>
     </row>
@@ -1835,22 +1835,22 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
@@ -1861,10 +1861,10 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F32" s="11"/>
     </row>
@@ -1877,22 +1877,22 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
     </row>
     <row r="35" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
@@ -1903,10 +1903,10 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F35" s="11"/>
     </row>
@@ -1919,10 +1919,10 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F36" s="11"/>
     </row>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
     </row>
     <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
@@ -1961,10 +1961,10 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F39" s="11"/>
     </row>
@@ -1977,10 +1977,10 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F40" s="11"/>
     </row>
@@ -1993,10 +1993,10 @@
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F41" s="11"/>
     </row>
@@ -2040,12 +2040,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
